--- a/stories/arbres/ATOM-TMP.MET.001-05.xlsx
+++ b/stories/arbres/ATOM-TMP.MET.001-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Gauthier veut sortir avec maman. Il fait froid. Maman prend le manteau. Gauthier enfile le manteau. Le tissu est chaud. Maman dit : froid, le manteau. Ils vont jusqu'au portail. Plus tard, le ciel devient gris. Dehors, il y a de la pluie. Maman prend les bottes. Gauthier met les bottes. Ses pieds sont au sec. Maman dit : pluie, les bottes. Ils marchent. Gauthier entend la pluie. Plic ploc. Le manteau le tient au chaud. Les bottes gardent les pieds secs. Le soir, Gauthier range le manteau. Il range aussi les bottes. Maman dit : demain, on regardera encore. Froid, le manteau. Pluie, les bottes. Gauthier hoche la tête. Il a compris.</t>
+          <t>Gauthier veut sortir avec maman. Il fait froid. Maman prend le manteau. Gauthier enfile le manteau. Le tissu est chaud. Froid, le manteau. Ils vont jusqu'au portail. Plus tard, le ciel devient gris. Dehors, il y a de la pluie. Maman prend les bottes. Gauthier met les bottes. Ses pieds sont au sec. Pluie, les bottes. Ils marchent. Gauthier entend la pluie. Plic ploc. Le manteau le tient au chaud. Les bottes gardent les pieds secs. Le soir, Gauthier range le manteau. Il range aussi les bottes. Demain, on regardera encore. Froid, le manteau. Pluie, les bottes. Gauthier hoche la tête. Il a compris.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Gauthier veut sortir avec maman. Il fait froid. Maman prend le manteau. Gauthier enfile le manteau. Le tissu est chaud.
+maman|Froid, le manteau. Ils vont jusqu'au portail. Plus tard, le ciel devient gris. Dehors, il y a de la pluie. Maman prend les bottes.
+narrateur|Gauthier met les bottes. Ses pieds sont au sec.
+maman|Pluie, les bottes.
+narrateur|Ils marchent. Gauthier entend la pluie. Plic ploc. Le manteau le tient au chaud. Les bottes gardent les pieds secs. Le soir, Gauthier range le manteau. Il range aussi les bottes.
+maman|Demain, on regardera encore. Froid, le manteau. Pluie, les bottes.
+narrateur|Gauthier hoche la tête. Il a compris.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Il pleut. Que met Gauthier ?</t>
         </is>
       </c>
     </row>
@@ -1629,6 +1661,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Gauthier a mis le manteau. Il a mis les bottes. Maman était là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1828,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Gauthier entend encore la pluie. Ses pieds restent au sec.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1995,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2035,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-TMP.MET.001-05.xlsx
+++ b/stories/arbres/ATOM-TMP.MET.001-05.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,7 @@
 narrateur|Gauthier hoche la tête. Il a compris.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1505,7 @@
           <t>narrateur|Il pleut. Que met Gauthier ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1666,6 +1673,7 @@
           <t>narrateur|Gauthier a mis le manteau. Il a mis les bottes. Maman était là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1841,7 @@
           <t>narrateur|Gauthier entend encore la pluie. Ses pieds restent au sec.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2000,6 +2009,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2018,7 +2028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2042,6 +2052,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2243,6 +2267,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-TMP.MET.001-05.xlsx
+++ b/stories/arbres/ATOM-TMP.MET.001-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Gauthier choisit manteau et bottes</t>
+          <t>Le bon manteau du square</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Chouchou veut le square mouillé. Le premier manteau est trop petit. Elle prend le bon. Elles vont au tourniquet qui goutte. Chouchou tourne.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Gauthier veut sortir avec maman. Il fait froid. Maman prend le manteau. Gauthier enfile le manteau. Le tissu est chaud. Froid, le manteau. Ils vont jusqu'au portail. Plus tard, le ciel devient gris. Dehors, il y a de la pluie. Maman prend les bottes. Gauthier met les bottes. Ses pieds sont au sec. Pluie, les bottes. Ils marchent. Gauthier entend la pluie. Plic ploc. Le manteau le tient au chaud. Les bottes gardent les pieds secs. Le soir, Gauthier range le manteau. Il range aussi les bottes. Demain, on regardera encore. Froid, le manteau. Pluie, les bottes. Gauthier hoche la tête. Il a compris.</t>
+          <t>Le tourniquet du square goutte encore. Les barres brillent, toutes sombres. L'odeur de terre mouillée entre par la porte. Chouchou vit ici, avec maman. Le square est juste après le passage. Je veux le tourniquet. Il a plu, tu as vu ? Oui. Il goutte. On se couvre, alors. En ce moment, Chouchou prend un manteau sur le crochet. C'est le rouge, le plus près. Elle passe un bras. L'autre bras résiste. Il est bizarre. Les manches s'arrêtent trop tôt. Il est trop petit, tu sens ? Chouchou le retire. Le rouge retombe sur le crochet. Maman tend l'autre, le bleu. Chouchou glisse les deux bras. Les manches arrivent aux poignets. Celui-là, oui. Le bon. Chouchou enfile les bottes près du paillasson. Elles sont encore un peu humides. Prête pour le square ? Oui ! Elles sortent. Le passage sent la pierre mouillée. Une flaque barre une dalle. Chouchou la contourne. Le square s'ouvre, tout luisant. Le tourniquet tourne tout seul, un peu, sous le vent. Il m'attend. Tu y vas ? Chouchou pose les mains sur une barre. C'est froid, et mouillé. Elle pousse. Le tourniquet part. Ça glisse ! Bravo. Tu l'as fait démarrer. L'eau saute des barres. Le manteau bleu la reçoit. Chouchou a chaud dedans.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Gauthier veut sortir avec maman. Il fait &lt;emphasis level="moderate"&gt;froid&lt;/emphasis&gt;. Maman prend le manteau. Gauthier enfile le manteau. Le tissu est chaud. Maman dit : froid, le manteau. Ils vont jusqu'au portail. Plus tard, le ciel devient gris. Dehors, il y a de la pluie. Maman prend les bottes. Gauthier met les bottes. Ses pieds sont au sec. Maman dit : pluie, les bottes. Ils marchent. Gauthier entend la pluie. Plic ploc. Le manteau le tient au chaud. Les bottes gardent les pieds secs. Le soir, Gauthier range le manteau. Il range aussi les bottes. Maman dit : demain, on regardera encore. Froid, le manteau. Pluie, les bottes. Gauthier hoche la tête. Il a compris.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le tourniquet du square goutte encore. Les barres brillent, toutes sombres. L'odeur de terre mouillée entre par la porte. Chouchou vit ici, avec maman. Le square est juste après le passage. Je veux le tourniquet. Il a plu, tu as vu ? Oui. Il goutte. On se couvre, alors. En ce moment, Chouchou prend un manteau sur le crochet. C'est le rouge, le plus près. Elle passe un bras. L'autre bras résiste. Il est bizarre. Les manches s'arrêtent trop tôt. Il est trop petit, tu sens ? Chouchou le retire. Le rouge retombe sur le crochet. Maman tend l'autre, le bleu. Chouchou glisse les deux bras. Les manches arrivent aux poignets. Celui-là, oui. Le bon. Chouchou enfile les bottes près du paillasson. Elles sont encore un peu humides. Prête pour le square ? Oui ! Elles sortent. Le passage sent la pierre mouillée. Une flaque barre une dalle. Chouchou la contourne. Le square s'ouvre, tout luisant. Le tourniquet tourne tout seul, un peu, sous le vent. Il m'attend. Tu y vas ? Chouchou pose les mains sur une barre. C'est froid, et mouillé. Elle pousse. Le tourniquet part. Ça glisse ! Bravo. Tu l'as fait démarrer. L'eau saute des barres. Le manteau bleu la reçoit. Chouchou a chaud dedans.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.96</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,16 +1324,54 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Gauthier veut sortir avec maman. Il fait froid. Maman prend le manteau. Gauthier enfile le manteau. Le tissu est chaud.
-maman|Froid, le manteau. Ils vont jusqu'au portail. Plus tard, le ciel devient gris. Dehors, il y a de la pluie. Maman prend les bottes.
-narrateur|Gauthier met les bottes. Ses pieds sont au sec.
-maman|Pluie, les bottes.
-narrateur|Ils marchent. Gauthier entend la pluie. Plic ploc. Le manteau le tient au chaud. Les bottes gardent les pieds secs. Le soir, Gauthier range le manteau. Il range aussi les bottes.
-maman|Demain, on regardera encore. Froid, le manteau. Pluie, les bottes.
-narrateur|Gauthier hoche la tête. Il a compris.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Le tourniquet du square goutte encore.
+narrateur|Les barres brillent, toutes sombres.
+narrateur|L'odeur de terre mouillée entre par la porte.
+narrateur|Chouchou vit ici, avec maman.
+narrateur|Le square est juste après le passage.
+enfant-f|Je veux le tourniquet.
+maman|Il a plu, tu as vu ?
+enfant-f|Oui.
+enfant-f|Il goutte.
+maman|On se couvre, alors.
+narrateur|En ce moment, Chouchou prend un manteau sur le crochet.
+narrateur|C'est le rouge, le plus près.
+narrateur|Elle passe un bras.
+narrateur|L'autre bras résiste.
+enfant-f|Il est bizarre.
+maman|Les manches s'arrêtent trop tôt.
+maman|Il est trop petit, tu sens ?
+narrateur|Chouchou le retire.
+narrateur|Le rouge retombe sur le crochet.
+narrateur|Maman tend l'autre, le bleu.
+narrateur|Chouchou glisse les deux bras.
+narrateur|Les manches arrivent aux poignets.
+enfant-f|Celui-là, oui.
+maman|Le bon.
+narrateur|Chouchou enfile les bottes près du paillasson.
+narrateur|Elles sont encore un peu humides.
+maman|Prête pour le square ?
+enfant-f|Oui !
+narrateur|Elles sortent.
+narrateur|Le passage sent la pierre mouillée.
+narrateur|Une flaque barre une dalle.
+narrateur|Chouchou la contourne.
+narrateur|Le square s'ouvre, tout luisant.
+narrateur|Le tourniquet tourne tout seul, un peu, sous le vent.
+enfant-f|Il m'attend.
+maman|Tu y vas ?
+narrateur|Chouchou pose les mains sur une barre.
+narrateur|C'est froid, et mouillé.
+narrateur|Elle pousse.
+narrateur|Le tourniquet part.
+enfant-f|Ça glisse !
+maman|Bravo.
+maman|Tu l'as fait démarrer.
+narrateur|L'eau saute des barres.
+narrateur|Le manteau bleu la reçoit.
+narrateur|Chouchou a chaud dedans.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1346,19 +1396,19 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>Il a plu, le square est mouillé. Que met Chouchou ?</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Il a plu, le square est mouillé. Que met Chouchou ?</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
           <t>Il pleut. Que met Gauthier ?</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Il pleut. Que met Gauthier ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Il pleut. Que met Gauthier ?</t>
-        </is>
-      </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>bottes</t>
@@ -1381,7 +1431,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Il met les bottes. Que met Gauthier s'il pleut ?</t>
+          <t>Il met les bottes. Que met Chouchou s'il pleut ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1423,14 +1473,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA3" s="2" t="n">
         <v>0.9</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1502,10 +1552,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Il pleut. Que met Gauthier ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Il a plu, le square est mouillé.
+narrateur|Que met Chouchou ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1530,12 +1580,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Gauthier a mis le manteau. Il a mis les bottes. Maman était là.</t>
+          <t>Chouchou tourne encore. Les bottes tapent les dalles mouillées. Plus vite ! Un peu, pas trop. Le tourniquet chante, tout rouillé. Une goutte part d'une barre. Elle atterrit sur le nez de Chouchou. Ah ! Le square te salue. Chouchou ralentit. Elle descend. Ses joues sont rouges. Le manteau bleu est mouillé aux manches. Les manches, assez longues, l'ont protégée. Le rouge n'aurait pas suffi. Tu as bien choisi. Elles vont jusqu'au banc. Le bois est sombre, encore plein d'eau. On s'assoit un moment ? Oui. Chouchou s'assoit au bord. Le tourniquet s'arrête, goutte encore.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Gauthier a mis le manteau. Il a mis les bottes. Maman était là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Chouchou tourne encore. Les bottes tapent les dalles mouillées. Plus vite ! Un peu, pas trop. Le tourniquet chante, tout rouillé. Une goutte part d'une barre. Elle atterrit sur le nez de Chouchou. Ah ! Le square te salue. Chouchou ralentit. Elle descend. Ses joues sont rouges. Le manteau bleu est mouillé aux manches. Les manches, assez longues, l'ont protégée. Le rouge n'aurait pas suffi. Tu as bien choisi. Elles vont jusqu'au banc. Le bois est sombre, encore plein d'eau. On s'assoit un moment ? Oui. Chouchou s'assoit au bord. Le tourniquet s'arrête, goutte encore.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1598,7 +1648,7 @@
         <v>0.96</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1670,10 +1720,30 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Gauthier a mis le manteau. Il a mis les bottes. Maman était là.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Chouchou tourne encore.
+narrateur|Les bottes tapent les dalles mouillées.
+enfant-f|Plus vite !
+maman|Un peu, pas trop.
+narrateur|Le tourniquet chante, tout rouillé.
+narrateur|Une goutte part d'une barre.
+narrateur|Elle atterrit sur le nez de Chouchou.
+enfant-f|Ah !
+maman|Le square te salue.
+narrateur|Chouchou ralentit.
+narrateur|Elle descend.
+narrateur|Ses joues sont rouges.
+narrateur|Le manteau bleu est mouillé aux manches.
+narrateur|Les manches, assez longues, l'ont protégée.
+enfant-f|Le rouge n'aurait pas suffi.
+maman|Tu as bien choisi.
+narrateur|Elles vont jusqu'au banc.
+narrateur|Le bois est sombre, encore plein d'eau.
+maman|On s'assoit un moment ?
+enfant-f|Oui.
+narrateur|Chouchou s'assoit au bord.
+narrateur|Le tourniquet s'arrête, goutte encore.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1698,12 +1768,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Gauthier entend encore la pluie. Ses pieds restent au sec.</t>
+          <t>Elles rentrent par le passage. Chouchou retire le manteau bleu. Le rouge reste au crochet ? Pour plus tard. Les bottes s'alignent près du paillasson. De l'eau de square s'égoutte.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Gauthier entend encore la &lt;emphasis level="moderate"&gt;pluie&lt;/emphasis&gt;. Ses pieds restent au sec.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Elles rentrent par le passage. Chouchou retire le manteau bleu. Le rouge reste au crochet ? Pour plus tard. Les bottes s'alignent près du paillasson. De l'eau de square s'égoutte.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1766,7 +1836,7 @@
         <v>0.96</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1838,10 +1908,14 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Gauthier entend encore la pluie. Ses pieds restent au sec.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Elles rentrent par le passage.
+narrateur|Chouchou retire le manteau bleu.
+maman|Le rouge reste au crochet ?
+enfant-f|Pour plus tard.
+narrateur|Les bottes s'alignent près du paillasson.
+narrateur|De l'eau de square s'égoutte.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1866,12 +1940,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Au square, le tourniquet goutte encore. Les barres brillent, plus calmes. Il m'a attendue. Oui. Le manteau bleu sèche, les manches longues.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Au square, le tourniquet goutte encore. Les barres brillent, plus calmes. Il m'a attendue. Oui. Le manteau bleu sèche, les manches longues.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1934,7 +2008,7 @@
         <v>0.92</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2006,10 +2080,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Au square, le tourniquet goutte encore.
+narrateur|Les barres brillent, plus calmes.
+enfant-f|Il m'a attendue.
+maman|Oui.
+narrateur|Le manteau bleu sèche, les manches longues.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2028,7 +2105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2066,6 +2143,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-TMP.MET.001-05.xlsx
+++ b/stories/arbres/ATOM-TMP.MET.001-05.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>entrée de la maison</t>
+          <t>entrée puis square mouillé après la pluie</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Gauthier, maman</t>
+          <t>Chouchou, maman</t>
         </is>
       </c>
     </row>
